--- a/outputs/analysis/analysis_output/tables/part2/benefit_presence_summary.xlsx
+++ b/outputs/analysis/analysis_output/tables/part2/benefit_presence_summary.xlsx
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99.17144678138942</v>
+        <v>98.6468200270636</v>
       </c>
       <c r="C2" t="n">
-        <v>1556</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="3">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98.91650732950924</v>
+        <v>99.3234100135318</v>
       </c>
       <c r="C3" t="n">
-        <v>1552</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="4">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>99.36265137029955</v>
+        <v>99.25575101488498</v>
       </c>
       <c r="C4" t="n">
-        <v>1559</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="5">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.87253027405991</v>
+        <v>98.51150202976996</v>
       </c>
       <c r="C5" t="n">
-        <v>1567</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="6">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99.74506054811982</v>
+        <v>98.57916102841678</v>
       </c>
       <c r="C6" t="n">
-        <v>1565</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="7">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.151051625239</v>
+        <v>31.32611637347767</v>
       </c>
       <c r="C7" t="n">
-        <v>426</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
